--- a/experiment/ELAN_bestx2/Test/results-Manga109/Manga109.xlsx
+++ b/experiment/ELAN_bestx2/Test/results-Manga109/Manga109.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.44</v>
+        <v>35.8</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9136</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.21</v>
+        <v>36.83</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9341</v>
+        <v>0.9465</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.48</v>
+        <v>37.15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9778</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.59</v>
+        <v>43.92</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9789</v>
+        <v>0.9878</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38.68</v>
+        <v>44.77</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9839</v>
+        <v>0.9931</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.32</v>
+        <v>37.59</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9537</v>
+        <v>0.9799</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34.83</v>
+        <v>41.68</v>
       </c>
       <c r="C8" t="n">
-        <v>0.972</v>
+        <v>0.9868</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.13</v>
+        <v>34.29</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.971</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31.87</v>
+        <v>38.47</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9539</v>
+        <v>0.9838</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31.05</v>
+        <v>37.39</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9362</v>
+        <v>0.9648</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31.36</v>
+        <v>38.72</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9619</v>
+        <v>0.9887</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31.01</v>
+        <v>36.09</v>
       </c>
       <c r="C13" t="n">
-        <v>0.944</v>
+        <v>0.9707</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33.56</v>
+        <v>41.48</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9676</v>
+        <v>0.9909</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31.95</v>
+        <v>38.62</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9452</v>
+        <v>0.9671999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32.28</v>
+        <v>38.61</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9587</v>
+        <v>0.9833</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.68</v>
+        <v>36.47</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9519</v>
+        <v>0.9822</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31.43</v>
+        <v>39.39</v>
       </c>
       <c r="C18" t="n">
-        <v>0.96</v>
+        <v>0.9899</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>35.81</v>
+        <v>43.48</v>
       </c>
       <c r="C19" t="n">
-        <v>0.984</v>
+        <v>0.9944</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>33.47</v>
+        <v>38.39</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9547</v>
+        <v>0.9751</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>33.87</v>
+        <v>42.1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.98</v>
+        <v>0.9946</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33.57</v>
+        <v>39.69</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9612000000000001</v>
+        <v>0.9815</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>33.33</v>
+        <v>39.66</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9839</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32.23</v>
+        <v>38.64</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9532</v>
+        <v>0.9805</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>36.59</v>
+        <v>44.34</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9771</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29.88</v>
+        <v>37.9</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9641</v>
+        <v>0.9898</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>33.47</v>
+        <v>39.35</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9657</v>
+        <v>0.9864000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>37.97</v>
+        <v>44.62</v>
       </c>
       <c r="C28" t="n">
-        <v>0.983</v>
+        <v>0.9925</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>34.2</v>
+        <v>38.55</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9639</v>
+        <v>0.9811</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>34.85</v>
+        <v>41.79</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9731</v>
+        <v>0.9893999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>33.74</v>
+        <v>39.43</v>
       </c>
       <c r="C31" t="n">
-        <v>0.967</v>
+        <v>0.9855</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28.95</v>
+        <v>36.8</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9883</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.03</v>
+        <v>37.08</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9484</v>
+        <v>0.9861</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>35.04</v>
+        <v>40.1</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9538</v>
+        <v>0.9779</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>31.02</v>
+        <v>34.31</v>
       </c>
       <c r="C35" t="n">
-        <v>0.888</v>
+        <v>0.9189000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.73</v>
+        <v>33.75</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9418</v>
+        <v>0.9705</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>33.89</v>
+        <v>39.5</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9794</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>28.54</v>
+        <v>33.02</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9004</v>
+        <v>0.9385</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>34.64</v>
+        <v>42.38</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9757</v>
+        <v>0.9919</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>36.74</v>
+        <v>42.99</v>
       </c>
       <c r="C40" t="n">
-        <v>0.977</v>
+        <v>0.9905</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29.32</v>
+        <v>35.7</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9246</v>
+        <v>0.9713000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.97</v>
+        <v>38.19</v>
       </c>
       <c r="C42" t="n">
-        <v>0.9266</v>
+        <v>0.9677</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>34.4</v>
+        <v>40.47</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9607</v>
+        <v>0.9806</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>23.8</v>
+        <v>29.12</v>
       </c>
       <c r="C44" t="n">
-        <v>0.8715000000000001</v>
+        <v>0.9515</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>37.55</v>
+        <v>44.31</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9853</v>
+        <v>0.9959</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>25.7</v>
+        <v>30.21</v>
       </c>
       <c r="C46" t="n">
-        <v>0.9313</v>
+        <v>0.9641999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>30.77</v>
+        <v>36.55</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9499</v>
+        <v>0.9806</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>36.21</v>
+        <v>41.39</v>
       </c>
       <c r="C48" t="n">
-        <v>0.969</v>
+        <v>0.9869</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28.59</v>
+        <v>34.65</v>
       </c>
       <c r="C49" t="n">
-        <v>0.9173</v>
+        <v>0.9599</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>31.19</v>
+        <v>37.74</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9525</v>
+        <v>0.9837</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>28.03</v>
+        <v>32.5</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8509</v>
+        <v>0.8969</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>30.57</v>
+        <v>38.23</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9597</v>
+        <v>0.9845</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>34.67</v>
+        <v>40.98</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9665</v>
+        <v>0.9865</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>40.14</v>
+        <v>42.17</v>
       </c>
       <c r="C54" t="n">
-        <v>0.9583</v>
+        <v>0.9689</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>36.11</v>
+        <v>43.42</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9748</v>
+        <v>0.9902</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25.7</v>
+        <v>28.93</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8768</v>
+        <v>0.9356</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>35.05</v>
+        <v>42.88</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9785</v>
+        <v>0.9916</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>32.26</v>
+        <v>39.26</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9656</v>
+        <v>0.9841</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>32.98</v>
+        <v>40.18</v>
       </c>
       <c r="C59" t="n">
-        <v>0.9616</v>
+        <v>0.9875</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>25.41</v>
+        <v>29.24</v>
       </c>
       <c r="C60" t="n">
-        <v>0.8436</v>
+        <v>0.9221</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>34.19</v>
+        <v>40.63</v>
       </c>
       <c r="C61" t="n">
-        <v>0.9768</v>
+        <v>0.9898</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>33.92</v>
+        <v>40.96</v>
       </c>
       <c r="C62" t="n">
-        <v>0.972</v>
+        <v>0.9902</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>31.53</v>
+        <v>38.8</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9595</v>
+        <v>0.9865</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>35.84</v>
+        <v>41.77</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9755</v>
+        <v>0.9886</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>35.87</v>
+        <v>40.75</v>
       </c>
       <c r="C65" t="n">
-        <v>0.9601</v>
+        <v>0.9795</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.82</v>
+        <v>35.03</v>
       </c>
       <c r="C66" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.9872</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>34.37</v>
+        <v>40.69</v>
       </c>
       <c r="C67" t="n">
-        <v>0.9716</v>
+        <v>0.9879</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>34.24</v>
+        <v>40.6</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9618</v>
+        <v>0.9822</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>33.13</v>
+        <v>40.05</v>
       </c>
       <c r="C69" t="n">
-        <v>0.9607</v>
+        <v>0.9857</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>30.29</v>
+        <v>36.62</v>
       </c>
       <c r="C70" t="n">
-        <v>0.9483</v>
+        <v>0.9833</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>31.6</v>
+        <v>38.55</v>
       </c>
       <c r="C71" t="n">
-        <v>0.9579</v>
+        <v>0.9846</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>30.12</v>
+        <v>31.83</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8344</v>
+        <v>0.8504</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>35.97</v>
+        <v>42.62</v>
       </c>
       <c r="C73" t="n">
-        <v>0.9758</v>
+        <v>0.9905</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>35.82</v>
+        <v>41.74</v>
       </c>
       <c r="C74" t="n">
-        <v>0.9716</v>
+        <v>0.988</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>32.06</v>
+        <v>37.83</v>
       </c>
       <c r="C75" t="n">
-        <v>0.9597</v>
+        <v>0.9811</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>31.22</v>
+        <v>36.67</v>
       </c>
       <c r="C76" t="n">
-        <v>0.9414</v>
+        <v>0.9754</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>32.66</v>
+        <v>40.38</v>
       </c>
       <c r="C77" t="n">
-        <v>0.9671</v>
+        <v>0.9801</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>33.84</v>
+        <v>39.58</v>
       </c>
       <c r="C78" t="n">
-        <v>0.967</v>
+        <v>0.9831</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>28.8</v>
+        <v>33.2</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.9181</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>32.43</v>
+        <v>39.36</v>
       </c>
       <c r="C80" t="n">
-        <v>0.959</v>
+        <v>0.9878</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>33.39</v>
+        <v>39.92</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9661</v>
+        <v>0.9899</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>32.02</v>
+        <v>37.47</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9339</v>
+        <v>0.9698</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>34.48</v>
+        <v>39.24</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.9782</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>33.02</v>
+        <v>40.27</v>
       </c>
       <c r="C84" t="n">
-        <v>0.9735</v>
+        <v>0.9905</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>29.67</v>
+        <v>37.29</v>
       </c>
       <c r="C85" t="n">
-        <v>0.966</v>
+        <v>0.9883999999999999</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>34.24</v>
+        <v>40.81</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9651</v>
+        <v>0.9856</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>31.08</v>
+        <v>35.24</v>
       </c>
       <c r="C87" t="n">
-        <v>0.9435</v>
+        <v>0.9702</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>36.89</v>
+        <v>42.26</v>
       </c>
       <c r="C88" t="n">
-        <v>0.972</v>
+        <v>0.9871</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>34.45</v>
+        <v>41.76</v>
       </c>
       <c r="C89" t="n">
-        <v>0.9707</v>
+        <v>0.9888</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>31.44</v>
+        <v>37.98</v>
       </c>
       <c r="C90" t="n">
-        <v>0.9517</v>
+        <v>0.9802</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>25.59</v>
+        <v>32.18</v>
       </c>
       <c r="C91" t="n">
-        <v>0.8992</v>
+        <v>0.9519</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>30.38</v>
+        <v>37.57</v>
       </c>
       <c r="C92" t="n">
-        <v>0.9433</v>
+        <v>0.9839</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>28.07</v>
+        <v>37.22</v>
       </c>
       <c r="C93" t="n">
-        <v>0.9633</v>
+        <v>0.9927</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>22.77</v>
+        <v>27.39</v>
       </c>
       <c r="C94" t="n">
-        <v>0.8468</v>
+        <v>0.9324</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>35.64</v>
+        <v>42.51</v>
       </c>
       <c r="C95" t="n">
-        <v>0.9761</v>
+        <v>0.9901</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>27.78</v>
+        <v>34.48</v>
       </c>
       <c r="C96" t="n">
-        <v>0.9357</v>
+        <v>0.972</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>30.62</v>
+        <v>37.53</v>
       </c>
       <c r="C97" t="n">
-        <v>0.9479</v>
+        <v>0.9739</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>35.75</v>
+        <v>38.52</v>
       </c>
       <c r="C98" t="n">
-        <v>0.9533</v>
+        <v>0.9668</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>28.49</v>
+        <v>37.64</v>
       </c>
       <c r="C99" t="n">
-        <v>0.9578</v>
+        <v>0.9915</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>29.19</v>
+        <v>32.79</v>
       </c>
       <c r="C100" t="n">
-        <v>0.8893</v>
+        <v>0.9364</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>25.04</v>
+        <v>32.17</v>
       </c>
       <c r="C101" t="n">
-        <v>0.9173</v>
+        <v>0.9729</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>29.83</v>
+        <v>34.55</v>
       </c>
       <c r="C102" t="n">
-        <v>0.947</v>
+        <v>0.9774</v>
       </c>
     </row>
     <row r="103">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>30.25</v>
+        <v>35.46</v>
       </c>
       <c r="C103" t="n">
-        <v>0.9581</v>
+        <v>0.9856</v>
       </c>
     </row>
     <row r="104">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>37.92</v>
+        <v>44.58</v>
       </c>
       <c r="C104" t="n">
-        <v>0.9847</v>
+        <v>0.9927</v>
       </c>
     </row>
     <row r="105">
@@ -1791,10 +1791,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>31.84</v>
+        <v>38.23</v>
       </c>
       <c r="C105" t="n">
-        <v>0.955</v>
+        <v>0.9786</v>
       </c>
     </row>
     <row r="106">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>29.71</v>
+        <v>40.25</v>
       </c>
       <c r="C106" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.9893999999999999</v>
       </c>
     </row>
     <row r="107">
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>32</v>
+        <v>36.8</v>
       </c>
       <c r="C107" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9727</v>
       </c>
     </row>
     <row r="108">
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>39.8</v>
+        <v>43.28</v>
       </c>
       <c r="C108" t="n">
-        <v>0.9737</v>
+        <v>0.9821</v>
       </c>
     </row>
     <row r="109">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>34.9</v>
+        <v>38.74</v>
       </c>
       <c r="C109" t="n">
-        <v>0.9455</v>
+        <v>0.9681</v>
       </c>
     </row>
     <row r="110">
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>32.84</v>
+        <v>38.3</v>
       </c>
       <c r="C110" t="n">
-        <v>0.9678</v>
+        <v>0.9885</v>
       </c>
     </row>
     <row r="111">
@@ -1869,10 +1869,10 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>32.29</v>
+        <v>38.36</v>
       </c>
       <c r="C111" t="n">
-        <v>0.9496</v>
+        <v>0.9762</v>
       </c>
     </row>
   </sheetData>
